--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>c.1532</t>
+          <t>environ 1532</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>c.1508</t>
+          <t>environ 1508</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>c.1535</t>
+          <t>environ 1535</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>c.1535</t>
+          <t>environ 1535</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>c.1510</t>
+          <t>environ 1510</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>c.1540</t>
+          <t>environ 1540</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>c.1540-1549</t>
+          <t>environ 1540-1549</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>c.1488</t>
+          <t>environ 1488</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>c.1518</t>
+          <t>environ 1518</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>c.1533</t>
+          <t>environ 1533</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>c.1545</t>
+          <t>environ 1545</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>c.1545</t>
+          <t>environ 1545</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>c.1525</t>
+          <t>environ 1525</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>c.1525</t>
+          <t>environ 1525</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>c.1510</t>
+          <t>environ 1510</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>c.1485</t>
+          <t>environ 1485</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3665,17 +3665,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>c.1490</t>
+          <t>environ 1490</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>c.1560</t>
+          <t>environ 1560</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>c.1549-1550</t>
+          <t>environ 1549-1550</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>c.1545</t>
+          <t>environ 1545</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>c.1514-1519</t>
+          <t>environ 1514-1519</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>c.1509</t>
+          <t>environ 1509</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>c. 1504-1508</t>
+          <t>environ 1504-1508</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>c.1485</t>
+          <t>environ 1485</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>c.1520</t>
+          <t>environ 1520</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>c.1574</t>
+          <t>environ 1574</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>c.1561</t>
+          <t>environ 1561</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>c.1478</t>
+          <t>environ 1478</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>c.1470</t>
+          <t>environ 1470</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>c.1587</t>
+          <t>environ 1587</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>c.1490</t>
+          <t>environ 1490</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>c.1526</t>
+          <t>environ 1526</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>c.1534</t>
+          <t>environ 1534</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>c.1527-1531</t>
+          <t>environ 1527-1531</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>c.1519</t>
+          <t>environ 1519</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>c.1520</t>
+          <t>environ 1520</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>c.1580</t>
+          <t>environ 1580</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>c.1480</t>
+          <t>environ 1480</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>c.1531</t>
+          <t>environ 1531</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>c.1565</t>
+          <t>environ 1565</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>c.1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>c.1566</t>
+          <t>environ 1566</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>c.1488</t>
+          <t>environ 1488</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>c.1488</t>
+          <t>environ 1488</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>c.1488</t>
+          <t>environ 1488</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>c.1490</t>
+          <t>environ 1490</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9866,7 +9866,7 @@
       <c r="E129" s="1" t="n"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H129" s="1" t="inlineStr">
         <is>
-          <t>c.1509</t>
+          <t>environ 1509</t>
         </is>
       </c>
       <c r="I129" s="1" t="inlineStr">
@@ -9939,17 +9939,17 @@
       <c r="E130" s="1" t="n"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>c.1445</t>
+          <t>environ 1445</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>c.1503</t>
+          <t>environ 1503</t>
         </is>
       </c>
       <c r="H130" s="1" t="inlineStr">
         <is>
-          <t>c. 1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="I130" s="1" t="inlineStr">
@@ -10018,7 +10018,7 @@
       <c r="E131" s="1" t="n"/>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t>c.1490-1500</t>
+          <t>environ 1490-1500</t>
         </is>
       </c>
       <c r="I131" s="1" t="inlineStr">
@@ -10099,7 +10099,7 @@
       <c r="E132" s="1" t="n"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="H132" s="1" t="inlineStr">
         <is>
-          <t>c.1516</t>
+          <t>environ 1516</t>
         </is>
       </c>
       <c r="I132" s="1" t="inlineStr">
@@ -10176,7 +10176,7 @@
       <c r="E133" s="1" t="n"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="H133" s="1" t="inlineStr">
         <is>
-          <t>c.1490-1500</t>
+          <t>environ 1490-1500</t>
         </is>
       </c>
       <c r="I133" s="1" t="inlineStr">
@@ -10257,7 +10257,7 @@
       <c r="E134" s="1" t="n"/>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>c.1495-1500</t>
+          <t>environ 1495-1500</t>
         </is>
       </c>
       <c r="I134" s="1" t="inlineStr">
@@ -10338,7 +10338,7 @@
       <c r="E135" s="1" t="n"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>c.1490-1500</t>
+          <t>environ 1490-1500</t>
         </is>
       </c>
       <c r="I135" s="1" t="inlineStr">
@@ -10419,7 +10419,7 @@
       <c r="E136" s="1" t="n"/>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>c.1450</t>
+          <t>environ 1450</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>c.1490-1500</t>
+          <t>environ 1490-1500</t>
         </is>
       </c>
       <c r="I136" s="1" t="inlineStr">
@@ -10500,7 +10500,7 @@
       <c r="E137" s="1" t="n"/>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>c.1441</t>
+          <t>environ 1441</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
@@ -10573,7 +10573,7 @@
       <c r="E138" s="1" t="n"/>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>c.1454</t>
+          <t>environ 1454</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
@@ -10642,7 +10642,7 @@
       <c r="E139" s="1" t="n"/>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>c.1427</t>
+          <t>environ 1427</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>c.1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="I139" s="1" t="inlineStr">
@@ -10711,7 +10711,7 @@
       <c r="E140" s="1" t="n"/>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>c.1429</t>
+          <t>environ 1429</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
@@ -10788,7 +10788,7 @@
       <c r="E141" s="1" t="n"/>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="H141" s="1" t="inlineStr">
         <is>
-          <t>c.1510</t>
+          <t>environ 1510</t>
         </is>
       </c>
       <c r="I141" s="1" t="inlineStr">
@@ -10857,7 +10857,7 @@
       <c r="E142" s="1" t="n"/>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="H142" s="1" t="inlineStr">
         <is>
-          <t>c.1502-1507</t>
+          <t>environ 1502-1507</t>
         </is>
       </c>
       <c r="I142" s="1" t="inlineStr">
@@ -10926,7 +10926,7 @@
       <c r="E143" s="1" t="n"/>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t>c.1500</t>
+          <t>environ 1500</t>
         </is>
       </c>
       <c r="I143" s="1" t="inlineStr">
@@ -10995,7 +10995,7 @@
       <c r="E144" s="1" t="n"/>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="H144" s="1" t="inlineStr">
         <is>
-          <t>c.1515</t>
+          <t>environ 1515</t>
         </is>
       </c>
       <c r="I144" s="1" t="inlineStr">
@@ -11072,7 +11072,7 @@
       <c r="E145" s="1" t="n"/>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>c.1460</t>
+          <t>environ 1460</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
@@ -11149,7 +11149,7 @@
       <c r="E146" s="1" t="n"/>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
@@ -11226,7 +11226,7 @@
       <c r="E147" s="1" t="n"/>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
@@ -11303,7 +11303,7 @@
       <c r="E148" s="1" t="n"/>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>c.1430</t>
+          <t>environ 1430</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="H148" s="1" t="inlineStr">
         <is>
-          <t>c.1505</t>
+          <t>environ 1505</t>
         </is>
       </c>
       <c r="I148" s="1" t="inlineStr">

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Gallerie dell'Accademia</t>
+          <t>Les galeries de l'Académie</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Gallerie dell'Accademia</t>
+          <t>Les galeries de l'Académie</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Gallerie dell'Accademia</t>
+          <t>Les galeries de l'Académie</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Gallerie dell'Accademia</t>
+          <t>Les galeries de l'Académie</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Gallerie dell'Accademia</t>
+          <t>Les galeries de l'Académie</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6440C409-0A10-40CD-A4B6-97669C5CC132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E9363A-AFF2-4DB8-8871-E0355DEDE801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="1042">
   <si>
     <t>Prénom</t>
   </si>
@@ -1877,15 +1877,6 @@
   </si>
   <si>
     <t>Der zwölfjährige Jesus unter den Schriftgelehrten</t>
-  </si>
-  <si>
-    <t>"La Fête du Rosaire"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/Albrecht_D%C3%BCrer_-_Das_Rosenkranzfest_%281506%29.jpg/1280px-Albrecht_D%C3%BCrer_-_Das_Rosenkranzfest_%281506%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>194,5 cm</t>
   </si>
   <si>
     <t>Salle 054</t>
@@ -3494,7 +3485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X146"/>
+  <dimension ref="A1:X145"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7355,32 +7346,44 @@
       <c r="G85" t="s">
         <v>597</v>
       </c>
-      <c r="H85" t="s">
-        <v>170</v>
+      <c r="H85">
+        <v>1507</v>
+      </c>
+      <c r="I85" t="s">
+        <v>30</v>
       </c>
       <c r="J85" t="s">
-        <v>608</v>
+        <v>31</v>
+      </c>
+      <c r="L85" t="s">
+        <v>619</v>
       </c>
       <c r="M85" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N85" t="s">
+        <v>621</v>
+      </c>
+      <c r="O85" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q85" t="s">
         <v>620</v>
       </c>
       <c r="S85" t="s">
-        <v>85</v>
-      </c>
-      <c r="T85" t="s">
-        <v>381</v>
-      </c>
-      <c r="U85" t="s">
-        <v>621</v>
+        <v>623</v>
+      </c>
+      <c r="T85">
+        <v>209</v>
+      </c>
+      <c r="U85">
+        <v>81</v>
       </c>
       <c r="W85" t="s">
         <v>111</v>
       </c>
       <c r="X85">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7406,25 +7409,25 @@
         <v>31</v>
       </c>
       <c r="L86" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M86" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N86" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="O86" t="s">
         <v>625</v>
       </c>
       <c r="Q86" t="s">
+        <v>626</v>
+      </c>
+      <c r="S86" t="s">
         <v>623</v>
       </c>
-      <c r="S86" t="s">
-        <v>626</v>
-      </c>
       <c r="T86">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="U86">
         <v>81</v>
@@ -7450,37 +7453,37 @@
         <v>597</v>
       </c>
       <c r="H87">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="I87" t="s">
-        <v>30</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>31</v>
+        <v>627</v>
       </c>
       <c r="L87" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="M87" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N87" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="O87" t="s">
-        <v>628</v>
+        <v>555</v>
       </c>
       <c r="Q87" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="S87" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="T87">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="U87">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="W87" t="s">
         <v>111</v>
@@ -7503,37 +7506,37 @@
         <v>597</v>
       </c>
       <c r="H88">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="I88" t="s">
         <v>159</v>
       </c>
       <c r="J88" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L88" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M88" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N88" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O88" t="s">
         <v>555</v>
       </c>
       <c r="Q88" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="S88" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="T88">
-        <v>99</v>
-      </c>
-      <c r="U88">
-        <v>87</v>
+        <v>135</v>
+      </c>
+      <c r="U88" t="s">
+        <v>637</v>
       </c>
       <c r="W88" t="s">
         <v>111</v>
@@ -7555,38 +7558,29 @@
       <c r="G89" t="s">
         <v>597</v>
       </c>
-      <c r="H89">
-        <v>1511</v>
+      <c r="H89" t="s">
+        <v>131</v>
       </c>
       <c r="I89" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="J89" t="s">
-        <v>630</v>
-      </c>
-      <c r="L89" t="s">
-        <v>631</v>
+        <v>41</v>
       </c>
       <c r="M89" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N89" t="s">
-        <v>637</v>
-      </c>
-      <c r="O89" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="S89" t="s">
-        <v>639</v>
-      </c>
-      <c r="T89">
-        <v>135</v>
+        <v>85</v>
+      </c>
+      <c r="T89" t="s">
+        <v>640</v>
       </c>
       <c r="U89" t="s">
-        <v>640</v>
+        <v>136</v>
       </c>
       <c r="W89" t="s">
         <v>111</v>
@@ -7597,79 +7591,79 @@
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="B90" t="s">
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="F90" t="s">
-        <v>596</v>
+        <v>642</v>
       </c>
       <c r="G90" t="s">
-        <v>597</v>
+        <v>643</v>
       </c>
       <c r="H90" t="s">
-        <v>131</v>
+        <v>644</v>
       </c>
       <c r="I90" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="J90" t="s">
-        <v>41</v>
+        <v>645</v>
       </c>
       <c r="M90" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="N90" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="S90" t="s">
         <v>85</v>
       </c>
-      <c r="T90" t="s">
-        <v>643</v>
-      </c>
-      <c r="U90" t="s">
-        <v>136</v>
-      </c>
       <c r="W90" t="s">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="X90">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>154</v>
+        <v>648</v>
       </c>
       <c r="B91" t="s">
+        <v>649</v>
+      </c>
+      <c r="F91" t="s">
+        <v>520</v>
+      </c>
+      <c r="G91" t="s">
+        <v>650</v>
+      </c>
+      <c r="H91" t="s">
         <v>644</v>
       </c>
-      <c r="F91" t="s">
-        <v>645</v>
-      </c>
-      <c r="G91" t="s">
-        <v>646</v>
-      </c>
-      <c r="H91" t="s">
-        <v>647</v>
-      </c>
       <c r="I91" t="s">
-        <v>104</v>
+        <v>651</v>
       </c>
       <c r="J91" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="M91" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="N91" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="S91" t="s">
         <v>85</v>
       </c>
+      <c r="T91" t="s">
+        <v>655</v>
+      </c>
+      <c r="U91" t="s">
+        <v>656</v>
+      </c>
       <c r="W91" t="s">
         <v>292</v>
       </c>
@@ -7679,43 +7673,46 @@
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B92" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="F92" t="s">
-        <v>520</v>
+        <v>659</v>
       </c>
       <c r="G92" t="s">
-        <v>653</v>
+        <v>28</v>
       </c>
       <c r="H92" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="I92" t="s">
-        <v>654</v>
+        <v>487</v>
       </c>
       <c r="J92" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M92" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N92" t="s">
-        <v>657</v>
+        <v>663</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>664</v>
       </c>
       <c r="S92" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="T92" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="U92" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="W92" t="s">
-        <v>292</v>
+        <v>74</v>
       </c>
       <c r="X92">
         <v>3</v>
@@ -7723,43 +7720,34 @@
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="B93" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="F93" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="G93" t="s">
-        <v>28</v>
+        <v>462</v>
       </c>
       <c r="H93" t="s">
-        <v>663</v>
+        <v>494</v>
       </c>
       <c r="I93" t="s">
-        <v>487</v>
+        <v>104</v>
       </c>
       <c r="J93" t="s">
-        <v>664</v>
+        <v>105</v>
       </c>
       <c r="M93" t="s">
-        <v>665</v>
+        <v>222</v>
       </c>
       <c r="N93" t="s">
-        <v>666</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="S93" t="s">
-        <v>35</v>
-      </c>
-      <c r="T93" t="s">
-        <v>668</v>
-      </c>
-      <c r="U93" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="W93" t="s">
         <v>74</v>
@@ -7770,37 +7758,46 @@
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B94" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F94" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G94" t="s">
-        <v>462</v>
+        <v>675</v>
       </c>
       <c r="H94" t="s">
-        <v>494</v>
+        <v>219</v>
       </c>
       <c r="I94" t="s">
         <v>104</v>
       </c>
       <c r="J94" t="s">
-        <v>105</v>
+        <v>645</v>
       </c>
       <c r="M94" t="s">
-        <v>222</v>
+        <v>676</v>
       </c>
       <c r="N94" t="s">
-        <v>673</v>
+        <v>677</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>678</v>
       </c>
       <c r="S94" t="s">
-        <v>674</v>
+        <v>35</v>
+      </c>
+      <c r="T94" t="s">
+        <v>679</v>
+      </c>
+      <c r="U94" t="s">
+        <v>680</v>
       </c>
       <c r="W94" t="s">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="X94">
         <v>3</v>
@@ -7808,43 +7805,49 @@
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B95" t="s">
-        <v>676</v>
+        <v>682</v>
+      </c>
+      <c r="D95" t="s">
+        <v>683</v>
+      </c>
+      <c r="E95" t="s">
+        <v>683</v>
       </c>
       <c r="F95" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="G95" t="s">
-        <v>678</v>
+        <v>478</v>
       </c>
       <c r="H95" t="s">
-        <v>219</v>
+        <v>103</v>
       </c>
       <c r="I95" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="J95" t="s">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="M95" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="N95" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="Q95" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="S95" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="T95" t="s">
-        <v>682</v>
+        <v>274</v>
       </c>
       <c r="U95" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="W95" t="s">
         <v>292</v>
@@ -7855,52 +7858,37 @@
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="B96" t="s">
-        <v>685</v>
-      </c>
-      <c r="D96" t="s">
-        <v>686</v>
-      </c>
-      <c r="E96" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="F96" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="G96" t="s">
-        <v>478</v>
+        <v>597</v>
       </c>
       <c r="H96" t="s">
-        <v>103</v>
+        <v>462</v>
       </c>
       <c r="I96" t="s">
-        <v>80</v>
+        <v>692</v>
       </c>
       <c r="J96" t="s">
-        <v>81</v>
+        <v>693</v>
       </c>
       <c r="M96" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="N96" t="s">
-        <v>689</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="S96" t="s">
-        <v>85</v>
-      </c>
-      <c r="T96" t="s">
-        <v>274</v>
-      </c>
-      <c r="U96" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="W96" t="s">
-        <v>292</v>
+        <v>111</v>
       </c>
       <c r="X96">
         <v>3</v>
@@ -7908,37 +7896,43 @@
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B97" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="F97" t="s">
-        <v>694</v>
+        <v>566</v>
       </c>
       <c r="G97" t="s">
-        <v>597</v>
+        <v>699</v>
       </c>
       <c r="H97" t="s">
-        <v>462</v>
+        <v>700</v>
       </c>
       <c r="I97" t="s">
-        <v>695</v>
+        <v>104</v>
       </c>
       <c r="J97" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="M97" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="N97" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="S97" t="s">
-        <v>699</v>
+        <v>704</v>
+      </c>
+      <c r="T97" t="s">
+        <v>705</v>
+      </c>
+      <c r="U97" t="s">
+        <v>706</v>
       </c>
       <c r="W97" t="s">
-        <v>111</v>
+        <v>707</v>
       </c>
       <c r="X97">
         <v>3</v>
@@ -7946,46 +7940,49 @@
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>700</v>
+        <v>154</v>
       </c>
       <c r="B98" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="F98" t="s">
-        <v>566</v>
+        <v>709</v>
       </c>
       <c r="G98" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="H98" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="I98" t="s">
-        <v>104</v>
+        <v>712</v>
       </c>
       <c r="J98" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="M98" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="N98" t="s">
-        <v>706</v>
+        <v>715</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>716</v>
       </c>
       <c r="S98" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="T98" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="U98" t="s">
-        <v>709</v>
+        <v>342</v>
       </c>
       <c r="W98" t="s">
-        <v>710</v>
+        <v>111</v>
       </c>
       <c r="X98">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7993,40 +7990,40 @@
         <v>154</v>
       </c>
       <c r="B99" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F99" t="s">
+        <v>709</v>
+      </c>
+      <c r="G99" t="s">
+        <v>710</v>
+      </c>
+      <c r="H99" t="s">
+        <v>493</v>
+      </c>
+      <c r="I99" t="s">
         <v>712</v>
       </c>
-      <c r="G99" t="s">
+      <c r="J99" t="s">
         <v>713</v>
       </c>
-      <c r="H99" t="s">
-        <v>714</v>
-      </c>
-      <c r="I99" t="s">
-        <v>715</v>
-      </c>
-      <c r="J99" t="s">
-        <v>716</v>
-      </c>
       <c r="M99" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N99" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="Q99" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="S99" t="s">
-        <v>720</v>
+        <v>85</v>
       </c>
       <c r="T99" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="U99" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="W99" t="s">
         <v>111</v>
@@ -8040,46 +8037,46 @@
         <v>154</v>
       </c>
       <c r="B100" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F100" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G100" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H100" t="s">
-        <v>493</v>
+        <v>723</v>
       </c>
       <c r="I100" t="s">
-        <v>715</v>
+        <v>104</v>
       </c>
       <c r="J100" t="s">
-        <v>716</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="N100" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="Q100" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="S100" t="s">
-        <v>85</v>
+        <v>727</v>
       </c>
       <c r="T100" t="s">
-        <v>725</v>
+        <v>576</v>
       </c>
       <c r="U100" t="s">
-        <v>316</v>
+        <v>728</v>
       </c>
       <c r="W100" t="s">
         <v>111</v>
       </c>
       <c r="X100">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8087,46 +8084,46 @@
         <v>154</v>
       </c>
       <c r="B101" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F101" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G101" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H101" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="I101" t="s">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="J101" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="M101" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="N101" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="Q101" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="S101" t="s">
-        <v>730</v>
+        <v>85</v>
       </c>
       <c r="T101" t="s">
-        <v>576</v>
+        <v>733</v>
       </c>
       <c r="U101" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="W101" t="s">
         <v>111</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8134,128 +8131,122 @@
         <v>154</v>
       </c>
       <c r="B102" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F102" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G102" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H102" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>736</v>
       </c>
       <c r="J102" t="s">
-        <v>160</v>
+        <v>737</v>
       </c>
       <c r="M102" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="N102" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="Q102" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="S102" t="s">
         <v>85</v>
       </c>
       <c r="T102" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="U102" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="W102" t="s">
         <v>111</v>
       </c>
       <c r="X102">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>154</v>
+        <v>453</v>
       </c>
       <c r="B103" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="F103" t="s">
-        <v>712</v>
+        <v>64</v>
       </c>
       <c r="G103" t="s">
-        <v>713</v>
+        <v>744</v>
       </c>
       <c r="H103" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="I103" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="J103" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="M103" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="N103" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="S103" t="s">
-        <v>85</v>
-      </c>
-      <c r="T103" t="s">
-        <v>744</v>
-      </c>
-      <c r="U103" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="W103" t="s">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="X103">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>453</v>
+        <v>751</v>
       </c>
       <c r="B104" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="F104" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="G104" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="H104" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="I104" t="s">
-        <v>749</v>
+        <v>67</v>
       </c>
       <c r="J104" t="s">
-        <v>750</v>
+        <v>68</v>
       </c>
       <c r="M104" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="N104" t="s">
-        <v>752</v>
+        <v>756</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>757</v>
       </c>
       <c r="S104" t="s">
-        <v>753</v>
+        <v>35</v>
       </c>
       <c r="W104" t="s">
-        <v>292</v>
+        <v>74</v>
       </c>
       <c r="X104">
         <v>3</v>
@@ -8263,151 +8254,157 @@
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B105" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F105" t="s">
         <v>101</v>
       </c>
       <c r="G105" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="H105" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="I105" t="s">
-        <v>67</v>
+        <v>759</v>
       </c>
       <c r="J105" t="s">
-        <v>68</v>
+        <v>760</v>
       </c>
       <c r="M105" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="N105" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="Q105" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="S105" t="s">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="T105" t="s">
+        <v>37</v>
+      </c>
+      <c r="U105" t="s">
+        <v>764</v>
       </c>
       <c r="W105" t="s">
         <v>74</v>
       </c>
       <c r="X105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>754</v>
+        <v>578</v>
       </c>
       <c r="B106" t="s">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="F106" t="s">
         <v>101</v>
       </c>
       <c r="G106" t="s">
-        <v>756</v>
+        <v>478</v>
       </c>
       <c r="H106" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="I106" t="s">
-        <v>762</v>
+        <v>487</v>
       </c>
       <c r="J106" t="s">
-        <v>763</v>
+        <v>661</v>
       </c>
       <c r="M106" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="N106" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="Q106" t="s">
-        <v>766</v>
+        <v>283</v>
       </c>
       <c r="S106" t="s">
         <v>85</v>
       </c>
       <c r="T106" t="s">
-        <v>37</v>
+        <v>769</v>
       </c>
       <c r="U106" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="W106" t="s">
         <v>74</v>
       </c>
       <c r="X106">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>578</v>
+        <v>771</v>
       </c>
       <c r="B107" t="s">
-        <v>768</v>
+        <v>772</v>
+      </c>
+      <c r="D107" t="s">
+        <v>773</v>
+      </c>
+      <c r="E107" t="s">
+        <v>774</v>
       </c>
       <c r="F107" t="s">
-        <v>101</v>
+        <v>347</v>
       </c>
       <c r="G107" t="s">
-        <v>478</v>
+        <v>590</v>
       </c>
       <c r="H107" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="I107" t="s">
-        <v>487</v>
+        <v>159</v>
       </c>
       <c r="J107" t="s">
-        <v>664</v>
+        <v>160</v>
       </c>
       <c r="M107" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="N107" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="Q107" t="s">
-        <v>283</v>
+        <v>778</v>
       </c>
       <c r="S107" t="s">
-        <v>85</v>
-      </c>
-      <c r="T107" t="s">
-        <v>772</v>
-      </c>
-      <c r="U107" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="W107" t="s">
         <v>74</v>
       </c>
       <c r="X107">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>771</v>
+      </c>
+      <c r="B108" t="s">
+        <v>772</v>
+      </c>
+      <c r="D108" t="s">
+        <v>773</v>
+      </c>
+      <c r="E108" t="s">
         <v>774</v>
-      </c>
-      <c r="B108" t="s">
-        <v>775</v>
-      </c>
-      <c r="D108" t="s">
-        <v>776</v>
-      </c>
-      <c r="E108" t="s">
-        <v>777</v>
       </c>
       <c r="F108" t="s">
         <v>347</v>
@@ -8416,45 +8413,51 @@
         <v>590</v>
       </c>
       <c r="H108" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="I108" t="s">
-        <v>159</v>
+        <v>781</v>
       </c>
       <c r="J108" t="s">
-        <v>160</v>
+        <v>782</v>
       </c>
       <c r="M108" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="N108" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="Q108" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="S108" t="s">
-        <v>782</v>
+        <v>35</v>
+      </c>
+      <c r="T108" t="s">
+        <v>785</v>
+      </c>
+      <c r="U108" t="s">
+        <v>786</v>
       </c>
       <c r="W108" t="s">
         <v>74</v>
       </c>
       <c r="X108">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>771</v>
+      </c>
+      <c r="B109" t="s">
+        <v>772</v>
+      </c>
+      <c r="D109" t="s">
+        <v>773</v>
+      </c>
+      <c r="E109" t="s">
         <v>774</v>
-      </c>
-      <c r="B109" t="s">
-        <v>775</v>
-      </c>
-      <c r="D109" t="s">
-        <v>776</v>
-      </c>
-      <c r="E109" t="s">
-        <v>777</v>
       </c>
       <c r="F109" t="s">
         <v>347</v>
@@ -8463,90 +8466,90 @@
         <v>590</v>
       </c>
       <c r="H109" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I109" t="s">
-        <v>784</v>
+        <v>209</v>
       </c>
       <c r="J109" t="s">
-        <v>785</v>
+        <v>210</v>
       </c>
       <c r="M109" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="N109" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="Q109" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="S109" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="T109" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="U109" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="W109" t="s">
         <v>74</v>
       </c>
       <c r="X109">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>774</v>
+        <v>382</v>
       </c>
       <c r="B110" t="s">
-        <v>775</v>
+        <v>793</v>
       </c>
       <c r="D110" t="s">
-        <v>776</v>
+        <v>794</v>
       </c>
       <c r="E110" t="s">
-        <v>777</v>
+        <v>795</v>
       </c>
       <c r="F110" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="G110" t="s">
-        <v>590</v>
+        <v>796</v>
       </c>
       <c r="H110" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="I110" t="s">
-        <v>209</v>
+        <v>487</v>
       </c>
       <c r="J110" t="s">
-        <v>210</v>
+        <v>798</v>
       </c>
       <c r="M110" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="N110" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="Q110" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="S110" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="T110" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="U110" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="W110" t="s">
         <v>74</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8554,52 +8557,52 @@
         <v>382</v>
       </c>
       <c r="B111" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D111" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E111" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F111" t="s">
         <v>294</v>
       </c>
       <c r="G111" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="H111" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="I111" t="s">
-        <v>487</v>
+        <v>804</v>
       </c>
       <c r="J111" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="M111" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="N111" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="Q111" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="S111" t="s">
         <v>35</v>
       </c>
       <c r="T111" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="U111" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="W111" t="s">
         <v>74</v>
       </c>
       <c r="X111">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8607,52 +8610,52 @@
         <v>382</v>
       </c>
       <c r="B112" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D112" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E112" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F112" t="s">
         <v>294</v>
       </c>
       <c r="G112" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="H112" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="I112" t="s">
-        <v>807</v>
+        <v>209</v>
       </c>
       <c r="J112" t="s">
-        <v>808</v>
+        <v>210</v>
       </c>
       <c r="M112" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="N112" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="Q112" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="S112" t="s">
         <v>35</v>
       </c>
       <c r="T112" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="U112" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="W112" t="s">
         <v>74</v>
       </c>
       <c r="X112">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8660,46 +8663,46 @@
         <v>382</v>
       </c>
       <c r="B113" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D113" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E113" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F113" t="s">
         <v>294</v>
       </c>
       <c r="G113" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="H113" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="I113" t="s">
-        <v>209</v>
+        <v>487</v>
       </c>
       <c r="J113" t="s">
-        <v>210</v>
+        <v>818</v>
       </c>
       <c r="M113" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="N113" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="Q113" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="S113" t="s">
         <v>35</v>
       </c>
       <c r="T113" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="U113" t="s">
-        <v>819</v>
+        <v>439</v>
       </c>
       <c r="W113" t="s">
         <v>74</v>
@@ -8710,99 +8713,87 @@
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>382</v>
+        <v>823</v>
       </c>
       <c r="B114" t="s">
-        <v>796</v>
-      </c>
-      <c r="D114" t="s">
-        <v>797</v>
-      </c>
-      <c r="E114" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="F114" t="s">
-        <v>294</v>
+        <v>825</v>
       </c>
       <c r="G114" t="s">
-        <v>799</v>
+        <v>571</v>
       </c>
       <c r="H114" t="s">
-        <v>820</v>
+        <v>238</v>
       </c>
       <c r="I114" t="s">
-        <v>487</v>
+        <v>139</v>
       </c>
       <c r="J114" t="s">
-        <v>821</v>
+        <v>140</v>
       </c>
       <c r="M114" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="N114" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="Q114" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="S114" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="T114" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="U114" t="s">
-        <v>439</v>
+        <v>602</v>
       </c>
       <c r="W114" t="s">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="X114">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B115" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F115" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="G115" t="s">
-        <v>571</v>
-      </c>
-      <c r="H115" t="s">
-        <v>238</v>
+        <v>833</v>
       </c>
       <c r="I115" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="J115" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="M115" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="N115" t="s">
-        <v>830</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="S115" t="s">
         <v>85</v>
       </c>
       <c r="T115" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="U115" t="s">
-        <v>602</v>
+        <v>837</v>
       </c>
       <c r="W115" t="s">
-        <v>292</v>
+        <v>88</v>
       </c>
       <c r="X115">
         <v>3</v>
@@ -8810,40 +8801,46 @@
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>833</v>
+        <v>586</v>
       </c>
       <c r="B116" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="F116" t="s">
-        <v>835</v>
+        <v>642</v>
       </c>
       <c r="G116" t="s">
-        <v>836</v>
+        <v>839</v>
+      </c>
+      <c r="H116" t="s">
+        <v>840</v>
       </c>
       <c r="I116" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="J116" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="M116" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="N116" t="s">
-        <v>838</v>
+        <v>842</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>843</v>
       </c>
       <c r="S116" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="T116" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="U116" t="s">
-        <v>840</v>
+        <v>543</v>
       </c>
       <c r="W116" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="X116">
         <v>3</v>
@@ -8851,43 +8848,43 @@
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>586</v>
+        <v>216</v>
       </c>
       <c r="B117" t="s">
-        <v>841</v>
+        <v>845</v>
+      </c>
+      <c r="D117" t="s">
+        <v>846</v>
+      </c>
+      <c r="E117" t="s">
+        <v>847</v>
       </c>
       <c r="F117" t="s">
-        <v>645</v>
+        <v>101</v>
       </c>
       <c r="G117" t="s">
-        <v>842</v>
+        <v>597</v>
       </c>
       <c r="H117" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="I117" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J117" t="s">
-        <v>105</v>
+        <v>849</v>
       </c>
       <c r="M117" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="N117" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="Q117" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="S117" t="s">
-        <v>35</v>
-      </c>
-      <c r="T117" t="s">
-        <v>847</v>
-      </c>
-      <c r="U117" t="s">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="W117" t="s">
         <v>74</v>
@@ -8898,46 +8895,40 @@
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>216</v>
+        <v>518</v>
       </c>
       <c r="B118" t="s">
-        <v>848</v>
-      </c>
-      <c r="D118" t="s">
-        <v>849</v>
-      </c>
-      <c r="E118" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="F118" t="s">
-        <v>101</v>
+        <v>456</v>
       </c>
       <c r="G118" t="s">
-        <v>597</v>
+        <v>854</v>
       </c>
       <c r="H118" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="I118" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="J118" t="s">
-        <v>852</v>
+        <v>31</v>
       </c>
       <c r="M118" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="N118" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="Q118" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="S118" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="W118" t="s">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="X118">
         <v>3</v>
@@ -8945,19 +8936,19 @@
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>518</v>
+        <v>285</v>
       </c>
       <c r="B119" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F119" t="s">
-        <v>456</v>
+        <v>101</v>
       </c>
       <c r="G119" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="H119" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="I119" t="s">
         <v>30</v>
@@ -8966,107 +8957,113 @@
         <v>31</v>
       </c>
       <c r="M119" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="N119" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="Q119" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="S119" t="s">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="T119" t="s">
+        <v>865</v>
+      </c>
+      <c r="U119" t="s">
+        <v>866</v>
       </c>
       <c r="W119" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="X119">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="B120" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="F120" t="s">
-        <v>101</v>
+        <v>589</v>
       </c>
       <c r="G120" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="H120" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="I120" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="J120" t="s">
-        <v>31</v>
+        <v>870</v>
       </c>
       <c r="M120" t="s">
-        <v>865</v>
+        <v>205</v>
       </c>
       <c r="N120" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="Q120" t="s">
-        <v>867</v>
+        <v>207</v>
       </c>
       <c r="S120" t="s">
         <v>85</v>
       </c>
-      <c r="T120" t="s">
-        <v>868</v>
-      </c>
-      <c r="U120" t="s">
-        <v>869</v>
-      </c>
       <c r="W120" t="s">
-        <v>292</v>
+        <v>74</v>
       </c>
       <c r="X120">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>216</v>
+        <v>441</v>
       </c>
       <c r="B121" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F121" t="s">
-        <v>589</v>
+        <v>873</v>
       </c>
       <c r="G121" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H121" t="s">
-        <v>872</v>
+        <v>494</v>
       </c>
       <c r="I121" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="J121" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="M121" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="N121" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="Q121" t="s">
-        <v>207</v>
+        <v>877</v>
       </c>
       <c r="S121" t="s">
-        <v>85</v>
+        <v>878</v>
+      </c>
+      <c r="T121" t="s">
+        <v>879</v>
+      </c>
+      <c r="U121">
+        <v>18</v>
       </c>
       <c r="W121" t="s">
-        <v>74</v>
+        <v>440</v>
       </c>
       <c r="X121">
         <v>3</v>
@@ -9074,46 +9071,34 @@
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>441</v>
+        <v>880</v>
       </c>
       <c r="B122" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="F122" t="s">
-        <v>876</v>
+        <v>604</v>
       </c>
       <c r="G122" t="s">
-        <v>877</v>
+        <v>650</v>
       </c>
       <c r="H122" t="s">
-        <v>494</v>
-      </c>
-      <c r="I122" t="s">
-        <v>55</v>
+        <v>882</v>
       </c>
       <c r="J122" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="M122" t="s">
-        <v>222</v>
+        <v>884</v>
       </c>
       <c r="N122" t="s">
-        <v>879</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="S122" t="s">
-        <v>881</v>
-      </c>
-      <c r="T122" t="s">
-        <v>882</v>
-      </c>
-      <c r="U122">
-        <v>18</v>
+        <v>886</v>
       </c>
       <c r="W122" t="s">
-        <v>440</v>
+        <v>74</v>
       </c>
       <c r="X122">
         <v>3</v>
@@ -9121,37 +9106,55 @@
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>883</v>
+        <v>216</v>
       </c>
       <c r="B123" t="s">
-        <v>884</v>
+        <v>887</v>
+      </c>
+      <c r="D123" t="s">
+        <v>888</v>
+      </c>
+      <c r="E123" t="s">
+        <v>889</v>
       </c>
       <c r="F123" t="s">
-        <v>604</v>
+        <v>890</v>
       </c>
       <c r="G123" t="s">
-        <v>653</v>
+        <v>797</v>
       </c>
       <c r="H123" t="s">
-        <v>885</v>
+        <v>891</v>
+      </c>
+      <c r="I123" t="s">
+        <v>178</v>
       </c>
       <c r="J123" t="s">
-        <v>886</v>
+        <v>179</v>
       </c>
       <c r="M123" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="N123" t="s">
-        <v>888</v>
+        <v>893</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>894</v>
       </c>
       <c r="S123" t="s">
-        <v>889</v>
+        <v>35</v>
+      </c>
+      <c r="T123" t="s">
+        <v>895</v>
+      </c>
+      <c r="U123" t="s">
+        <v>896</v>
       </c>
       <c r="W123" t="s">
         <v>74</v>
       </c>
       <c r="X123">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9159,46 +9162,46 @@
         <v>216</v>
       </c>
       <c r="B124" t="s">
+        <v>887</v>
+      </c>
+      <c r="D124" t="s">
+        <v>888</v>
+      </c>
+      <c r="E124" t="s">
+        <v>889</v>
+      </c>
+      <c r="F124" t="s">
         <v>890</v>
       </c>
-      <c r="D124" t="s">
-        <v>891</v>
-      </c>
-      <c r="E124" t="s">
-        <v>892</v>
-      </c>
-      <c r="F124" t="s">
-        <v>893</v>
-      </c>
       <c r="G124" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H124" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="I124" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="J124" t="s">
-        <v>179</v>
+        <v>31</v>
       </c>
       <c r="M124" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="N124" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="Q124" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="S124" t="s">
         <v>35</v>
       </c>
       <c r="T124" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="U124" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="W124" t="s">
         <v>74</v>
@@ -9212,46 +9215,43 @@
         <v>216</v>
       </c>
       <c r="B125" t="s">
+        <v>887</v>
+      </c>
+      <c r="D125" t="s">
+        <v>888</v>
+      </c>
+      <c r="E125" t="s">
+        <v>889</v>
+      </c>
+      <c r="F125" t="s">
         <v>890</v>
       </c>
-      <c r="D125" t="s">
-        <v>891</v>
-      </c>
-      <c r="E125" t="s">
-        <v>892</v>
-      </c>
-      <c r="F125" t="s">
-        <v>893</v>
-      </c>
       <c r="G125" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H125" t="s">
-        <v>900</v>
-      </c>
-      <c r="I125" t="s">
-        <v>30</v>
+        <v>368</v>
       </c>
       <c r="J125" t="s">
-        <v>31</v>
+        <v>903</v>
       </c>
       <c r="M125" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="N125" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="Q125" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="S125" t="s">
         <v>35</v>
       </c>
       <c r="T125" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="U125" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="W125" t="s">
         <v>74</v>
@@ -9265,43 +9265,46 @@
         <v>216</v>
       </c>
       <c r="B126" t="s">
+        <v>887</v>
+      </c>
+      <c r="D126" t="s">
+        <v>888</v>
+      </c>
+      <c r="E126" t="s">
+        <v>889</v>
+      </c>
+      <c r="F126" t="s">
         <v>890</v>
       </c>
-      <c r="D126" t="s">
-        <v>891</v>
-      </c>
-      <c r="E126" t="s">
-        <v>892</v>
-      </c>
-      <c r="F126" t="s">
-        <v>893</v>
-      </c>
       <c r="G126" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H126" t="s">
-        <v>368</v>
+        <v>78</v>
+      </c>
+      <c r="I126" t="s">
+        <v>104</v>
       </c>
       <c r="J126" t="s">
-        <v>906</v>
+        <v>105</v>
       </c>
       <c r="M126" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="N126" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="Q126" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="S126" t="s">
         <v>35</v>
       </c>
       <c r="T126" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="U126" t="s">
-        <v>911</v>
+        <v>547</v>
       </c>
       <c r="W126" t="s">
         <v>74</v>
@@ -9315,46 +9318,46 @@
         <v>216</v>
       </c>
       <c r="B127" t="s">
+        <v>887</v>
+      </c>
+      <c r="D127" t="s">
+        <v>888</v>
+      </c>
+      <c r="E127" t="s">
+        <v>889</v>
+      </c>
+      <c r="F127" t="s">
         <v>890</v>
       </c>
-      <c r="D127" t="s">
-        <v>891</v>
-      </c>
-      <c r="E127" t="s">
-        <v>892</v>
-      </c>
-      <c r="F127" t="s">
-        <v>893</v>
-      </c>
       <c r="G127" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H127" t="s">
-        <v>78</v>
+        <v>913</v>
       </c>
       <c r="I127" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="J127" t="s">
-        <v>105</v>
+        <v>914</v>
       </c>
       <c r="M127" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="N127" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="Q127" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="S127" t="s">
         <v>35</v>
       </c>
       <c r="T127" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="U127" t="s">
-        <v>547</v>
+        <v>919</v>
       </c>
       <c r="W127" t="s">
         <v>74</v>
@@ -9365,93 +9368,84 @@
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>216</v>
+        <v>920</v>
       </c>
       <c r="B128" t="s">
-        <v>890</v>
-      </c>
-      <c r="D128" t="s">
-        <v>891</v>
-      </c>
-      <c r="E128" t="s">
-        <v>892</v>
+        <v>921</v>
       </c>
       <c r="F128" t="s">
-        <v>893</v>
+        <v>922</v>
       </c>
       <c r="G128" t="s">
-        <v>800</v>
+        <v>527</v>
       </c>
       <c r="H128" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="I128" t="s">
-        <v>178</v>
+        <v>924</v>
       </c>
       <c r="J128" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="M128" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="N128" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="Q128" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="S128" t="s">
-        <v>35</v>
-      </c>
-      <c r="T128" t="s">
-        <v>921</v>
-      </c>
-      <c r="U128" t="s">
-        <v>922</v>
+        <v>398</v>
       </c>
       <c r="W128" t="s">
         <v>74</v>
       </c>
       <c r="X128">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>923</v>
+        <v>276</v>
       </c>
       <c r="B129" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="F129" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="G129" t="s">
-        <v>527</v>
+        <v>931</v>
       </c>
       <c r="H129" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="I129" t="s">
-        <v>927</v>
+        <v>30</v>
       </c>
       <c r="J129" t="s">
-        <v>928</v>
+        <v>31</v>
       </c>
       <c r="M129" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="N129" t="s">
-        <v>930</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="S129" t="s">
-        <v>398</v>
+        <v>35</v>
+      </c>
+      <c r="T129" t="s">
+        <v>354</v>
+      </c>
+      <c r="U129" t="s">
+        <v>935</v>
       </c>
       <c r="W129" t="s">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="X129">
         <v>3</v>
@@ -9459,90 +9453,96 @@
     </row>
     <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>276</v>
+        <v>936</v>
       </c>
       <c r="B130" t="s">
-        <v>932</v>
+        <v>937</v>
+      </c>
+      <c r="D130" t="s">
+        <v>938</v>
       </c>
       <c r="F130" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="G130" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="H130" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="I130" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="J130" t="s">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="M130" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="N130" t="s">
-        <v>937</v>
+        <v>943</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>944</v>
       </c>
       <c r="S130" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="T130" t="s">
-        <v>354</v>
+        <v>945</v>
       </c>
       <c r="U130" t="s">
-        <v>938</v>
+        <v>543</v>
       </c>
       <c r="W130" t="s">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="X130">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>936</v>
+      </c>
+      <c r="B131" t="s">
+        <v>937</v>
+      </c>
+      <c r="D131" t="s">
+        <v>938</v>
+      </c>
+      <c r="F131" t="s">
         <v>939</v>
       </c>
-      <c r="B131" t="s">
+      <c r="G131" t="s">
         <v>940</v>
       </c>
-      <c r="D131" t="s">
-        <v>941</v>
-      </c>
-      <c r="F131" t="s">
-        <v>942</v>
-      </c>
-      <c r="G131" t="s">
-        <v>943</v>
-      </c>
       <c r="H131" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="I131" t="s">
-        <v>209</v>
+        <v>393</v>
       </c>
       <c r="J131" t="s">
-        <v>210</v>
+        <v>947</v>
       </c>
       <c r="M131" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="N131" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="Q131" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="S131" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="T131" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="U131" t="s">
-        <v>543</v>
+        <v>952</v>
       </c>
       <c r="W131" t="s">
         <v>74</v>
@@ -9553,46 +9553,46 @@
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>936</v>
+      </c>
+      <c r="B132" t="s">
+        <v>937</v>
+      </c>
+      <c r="D132" t="s">
+        <v>938</v>
+      </c>
+      <c r="F132" t="s">
         <v>939</v>
       </c>
-      <c r="B132" t="s">
+      <c r="G132" t="s">
         <v>940</v>
       </c>
-      <c r="D132" t="s">
-        <v>941</v>
-      </c>
-      <c r="F132" t="s">
-        <v>942</v>
-      </c>
-      <c r="G132" t="s">
-        <v>943</v>
-      </c>
       <c r="H132" t="s">
-        <v>949</v>
+        <v>462</v>
       </c>
       <c r="I132" t="s">
-        <v>393</v>
+        <v>139</v>
       </c>
       <c r="J132" t="s">
-        <v>950</v>
+        <v>140</v>
       </c>
       <c r="M132" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="N132" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="Q132" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="S132" t="s">
-        <v>398</v>
+        <v>35</v>
       </c>
       <c r="T132" t="s">
-        <v>954</v>
+        <v>183</v>
       </c>
       <c r="U132" t="s">
-        <v>955</v>
+        <v>602</v>
       </c>
       <c r="W132" t="s">
         <v>74</v>
@@ -9603,88 +9603,79 @@
     </row>
     <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>939</v>
+        <v>956</v>
       </c>
       <c r="B133" t="s">
-        <v>940</v>
-      </c>
-      <c r="D133" t="s">
-        <v>941</v>
+        <v>957</v>
       </c>
       <c r="F133" t="s">
-        <v>942</v>
+        <v>958</v>
       </c>
       <c r="G133" t="s">
-        <v>943</v>
+        <v>493</v>
       </c>
       <c r="H133" t="s">
-        <v>462</v>
-      </c>
-      <c r="I133" t="s">
-        <v>139</v>
+        <v>959</v>
       </c>
       <c r="J133" t="s">
-        <v>140</v>
+        <v>960</v>
       </c>
       <c r="M133" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="N133" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="Q133" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="S133" t="s">
-        <v>35</v>
-      </c>
-      <c r="T133" t="s">
-        <v>183</v>
+        <v>398</v>
       </c>
       <c r="U133" t="s">
-        <v>602</v>
+        <v>964</v>
       </c>
       <c r="W133" t="s">
         <v>74</v>
       </c>
       <c r="X133">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="B134" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="F134" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="G134" t="s">
-        <v>493</v>
+        <v>968</v>
       </c>
       <c r="H134" t="s">
-        <v>962</v>
+        <v>969</v>
+      </c>
+      <c r="I134" t="s">
+        <v>970</v>
       </c>
       <c r="J134" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="M134" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="N134" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="Q134" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="S134" t="s">
         <v>398</v>
       </c>
-      <c r="U134" t="s">
-        <v>967</v>
-      </c>
       <c r="W134" t="s">
         <v>74</v>
       </c>
@@ -9694,40 +9685,37 @@
     </row>
     <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="B135" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="F135" t="s">
-        <v>970</v>
+        <v>744</v>
       </c>
       <c r="G135" t="s">
-        <v>971</v>
+        <v>92</v>
       </c>
       <c r="H135" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="I135" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="J135" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="M135" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="N135" t="s">
-        <v>976</v>
-      </c>
-      <c r="Q135" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="S135" t="s">
-        <v>398</v>
+        <v>85</v>
       </c>
       <c r="W135" t="s">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="X135">
         <v>3</v>
@@ -9735,37 +9723,43 @@
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B136" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="F136" t="s">
-        <v>747</v>
+        <v>984</v>
       </c>
       <c r="G136" t="s">
-        <v>92</v>
+        <v>288</v>
       </c>
       <c r="H136" t="s">
-        <v>980</v>
+        <v>456</v>
       </c>
       <c r="I136" t="s">
-        <v>981</v>
+        <v>746</v>
       </c>
       <c r="J136" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="M136" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="N136" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="S136" t="s">
         <v>85</v>
       </c>
+      <c r="T136" t="s">
+        <v>988</v>
+      </c>
+      <c r="U136" t="s">
+        <v>989</v>
+      </c>
       <c r="W136" t="s">
-        <v>292</v>
+        <v>88</v>
       </c>
       <c r="X136">
         <v>3</v>
@@ -9773,43 +9767,43 @@
     </row>
     <row r="137" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="B137" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="F137" t="s">
-        <v>987</v>
+        <v>597</v>
       </c>
       <c r="G137" t="s">
-        <v>288</v>
+        <v>992</v>
       </c>
       <c r="H137" t="s">
-        <v>456</v>
+        <v>891</v>
       </c>
       <c r="I137" t="s">
-        <v>749</v>
+        <v>712</v>
       </c>
       <c r="J137" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
       <c r="M137" t="s">
-        <v>989</v>
+        <v>994</v>
       </c>
       <c r="N137" t="s">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="S137" t="s">
         <v>85</v>
       </c>
       <c r="T137" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
       <c r="U137" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="W137" t="s">
-        <v>88</v>
+        <v>292</v>
       </c>
       <c r="X137">
         <v>3</v>
@@ -9817,41 +9811,38 @@
     </row>
     <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="B138" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F138" t="s">
-        <v>597</v>
+        <v>494</v>
       </c>
       <c r="G138" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="H138" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="I138" t="s">
-        <v>715</v>
+        <v>159</v>
       </c>
       <c r="J138" t="s">
-        <v>996</v>
+        <v>160</v>
       </c>
       <c r="M138" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="N138" t="s">
-        <v>998</v>
+        <v>1001</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>1002</v>
       </c>
       <c r="S138" t="s">
         <v>85</v>
       </c>
-      <c r="T138" t="s">
-        <v>999</v>
-      </c>
-      <c r="U138" t="s">
-        <v>1000</v>
-      </c>
       <c r="W138" t="s">
         <v>292</v>
       </c>
@@ -9861,40 +9852,40 @@
     </row>
     <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1001</v>
+        <v>453</v>
       </c>
       <c r="B139" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="F139" t="s">
-        <v>494</v>
+        <v>589</v>
       </c>
       <c r="G139" t="s">
-        <v>1002</v>
+        <v>723</v>
       </c>
       <c r="H139" t="s">
-        <v>894</v>
+        <v>1004</v>
       </c>
       <c r="I139" t="s">
-        <v>159</v>
+        <v>1005</v>
       </c>
       <c r="J139" t="s">
-        <v>160</v>
+        <v>1006</v>
       </c>
       <c r="M139" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="N139" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="Q139" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="S139" t="s">
         <v>85</v>
       </c>
       <c r="W139" t="s">
-        <v>292</v>
+        <v>88</v>
       </c>
       <c r="X139">
         <v>3</v>
@@ -9902,137 +9893,146 @@
     </row>
     <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>453</v>
+        <v>1010</v>
       </c>
       <c r="B140" t="s">
-        <v>1006</v>
+        <v>1011</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1012</v>
       </c>
       <c r="F140" t="s">
-        <v>589</v>
+        <v>278</v>
       </c>
       <c r="G140" t="s">
-        <v>726</v>
+        <v>833</v>
       </c>
       <c r="H140" t="s">
-        <v>1007</v>
+        <v>238</v>
       </c>
       <c r="I140" t="s">
-        <v>1008</v>
+        <v>487</v>
       </c>
       <c r="J140" t="s">
-        <v>1009</v>
+        <v>661</v>
       </c>
       <c r="M140" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="N140" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="Q140" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="S140" t="s">
-        <v>85</v>
+        <v>35</v>
+      </c>
+      <c r="T140" t="s">
+        <v>1016</v>
+      </c>
+      <c r="U140" t="s">
+        <v>1017</v>
       </c>
       <c r="W140" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="X140">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B141" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="D141" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="F141" t="s">
         <v>278</v>
       </c>
       <c r="G141" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="H141" t="s">
-        <v>238</v>
+        <v>1018</v>
       </c>
       <c r="I141" t="s">
-        <v>487</v>
+        <v>178</v>
       </c>
       <c r="J141" t="s">
-        <v>664</v>
+        <v>1019</v>
       </c>
       <c r="M141" t="s">
-        <v>1016</v>
+        <v>428</v>
       </c>
       <c r="N141" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="Q141" t="s">
-        <v>1018</v>
+        <v>430</v>
       </c>
       <c r="S141" t="s">
         <v>35</v>
       </c>
       <c r="T141" t="s">
-        <v>1019</v>
+        <v>431</v>
       </c>
       <c r="U141" t="s">
-        <v>1020</v>
+        <v>375</v>
       </c>
       <c r="W141" t="s">
         <v>74</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B142" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="D142" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="F142" t="s">
         <v>278</v>
       </c>
       <c r="G142" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="H142" t="s">
+        <v>102</v>
+      </c>
+      <c r="I142" t="s">
+        <v>209</v>
+      </c>
+      <c r="J142" t="s">
+        <v>210</v>
+      </c>
+      <c r="M142" t="s">
         <v>1021</v>
       </c>
-      <c r="I142" t="s">
-        <v>178</v>
-      </c>
-      <c r="J142" t="s">
+      <c r="N142" t="s">
         <v>1022</v>
       </c>
-      <c r="M142" t="s">
-        <v>428</v>
-      </c>
-      <c r="N142" t="s">
+      <c r="Q142" t="s">
         <v>1023</v>
-      </c>
-      <c r="Q142" t="s">
-        <v>430</v>
       </c>
       <c r="S142" t="s">
         <v>35</v>
       </c>
       <c r="T142" t="s">
-        <v>431</v>
+        <v>337</v>
       </c>
       <c r="U142" t="s">
-        <v>375</v>
+        <v>1024</v>
       </c>
       <c r="W142" t="s">
         <v>74</v>
@@ -10043,46 +10043,43 @@
     </row>
     <row r="143" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="B143" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D143" t="s">
-        <v>1015</v>
+        <v>1026</v>
       </c>
       <c r="F143" t="s">
-        <v>278</v>
+        <v>597</v>
       </c>
       <c r="G143" t="s">
-        <v>836</v>
+        <v>931</v>
       </c>
       <c r="H143" t="s">
-        <v>102</v>
+        <v>418</v>
       </c>
       <c r="I143" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="J143" t="s">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="M143" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="N143" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="Q143" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="S143" t="s">
         <v>35</v>
       </c>
       <c r="T143" t="s">
-        <v>337</v>
+        <v>1030</v>
       </c>
       <c r="U143" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="W143" t="s">
         <v>74</v>
@@ -10093,142 +10090,95 @@
     </row>
     <row r="144" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B144" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="F144" t="s">
         <v>597</v>
       </c>
       <c r="G144" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="H144" t="s">
-        <v>418</v>
+        <v>368</v>
       </c>
       <c r="I144" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="J144" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="M144" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="N144" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q144" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="S144" t="s">
         <v>35</v>
       </c>
       <c r="T144" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="U144" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="W144" t="s">
         <v>74</v>
       </c>
       <c r="X144">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B145" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="F145" t="s">
         <v>597</v>
       </c>
       <c r="G145" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="H145" t="s">
-        <v>368</v>
+        <v>138</v>
       </c>
       <c r="I145" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="J145" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="M145" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="N145" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="Q145" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="S145" t="s">
         <v>35</v>
       </c>
       <c r="T145" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="U145" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="W145" t="s">
         <v>74</v>
       </c>
       <c r="X145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B146" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F146" t="s">
-        <v>597</v>
-      </c>
-      <c r="G146" t="s">
-        <v>934</v>
-      </c>
-      <c r="H146" t="s">
-        <v>138</v>
-      </c>
-      <c r="I146" t="s">
-        <v>178</v>
-      </c>
-      <c r="J146" t="s">
-        <v>179</v>
-      </c>
-      <c r="M146" t="s">
-        <v>1040</v>
-      </c>
-      <c r="N146" t="s">
-        <v>1041</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>1042</v>
-      </c>
-      <c r="S146" t="s">
-        <v>35</v>
-      </c>
-      <c r="T146" t="s">
-        <v>1043</v>
-      </c>
-      <c r="U146" t="s">
-        <v>1044</v>
-      </c>
-      <c r="W146" t="s">
-        <v>74</v>
-      </c>
-      <c r="X146">
         <v>2</v>
       </c>
     </row>

--- a/quizzes/peinture-16e.xlsx
+++ b/quizzes/peinture-16e.xlsx
@@ -897,7 +897,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>environ 1490</t>
+          <t>1490 environ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>environ 1532</t>
+          <t>1532 environ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>environ 1508</t>
+          <t>1508 environ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>environ 1535</t>
+          <t>1535 environ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>environ 1535</t>
+          <t>1535 environ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>environ 1510</t>
+          <t>1510 environ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>environ 1540</t>
+          <t>1540 environ</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>environ 1540-1549</t>
+          <t>1540-1549 environ</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>environ 1429</t>
+          <t>1429 environ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>environ 1505</t>
+          <t>1505 environ</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>environ 1430</t>
+          <t>1430 environ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>environ 1488</t>
+          <t>1488 environ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>environ 1518</t>
+          <t>1518 environ</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>environ 1533</t>
+          <t>1533 environ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>environ 1490-1500</t>
+          <t>1490-1500 environ</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>environ 1490-1500</t>
+          <t>1490-1500 environ</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>environ 1490-1500</t>
+          <t>1490-1500 environ</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>environ 1490-1500</t>
+          <t>1490-1500 environ</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>environ 1495-1500</t>
+          <t>1495-1500 environ</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>environ 1450</t>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>environ 1516</t>
+          <t>1516 environ</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>environ 1545</t>
+          <t>1545 environ</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>environ 1545</t>
+          <t>1545 environ</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>environ 1525</t>
+          <t>1525 environ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>environ 1525</t>
+          <t>1525 environ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>environ 1510</t>
+          <t>1510 environ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>environ 1485</t>
+          <t>1485 environ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4807,17 +4807,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>environ 1490</t>
+          <t>1490 environ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>environ 1560</t>
+          <t>1560 environ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>environ 1549-1550</t>
+          <t>1549-1550 environ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>environ 1545</t>
+          <t>1545 environ</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>environ 1502-1507</t>
+          <t>1502-1507 environ</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>environ 1509</t>
+          <t>1509 environ</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>environ 1510</t>
+          <t>1510 environ</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>environ 1515</t>
+          <t>1515 environ</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>environ 1460</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>environ 1514-1519</t>
+          <t>1514-1519 environ</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>environ 1509</t>
+          <t>1509 environ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>environ 1504-1508</t>
+          <t>1504-1508 environ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>environ 1485</t>
+          <t>1485 environ</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>environ 1454</t>
+          <t>1454 environ</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>environ 1520</t>
+          <t>1520 environ</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>environ 1574</t>
+          <t>1574 environ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>environ 1427</t>
+          <t>1427 environ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>environ 1561</t>
+          <t>1561 environ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>environ 1478</t>
+          <t>1478 environ</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>environ 1470</t>
+          <t>1470 environ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>environ 1587</t>
+          <t>1587 environ</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>environ 1490</t>
+          <t>1490 environ</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>environ 1526</t>
+          <t>1526 environ</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>environ 1534</t>
+          <t>1534 environ</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>environ 1527-1531</t>
+          <t>1527-1531 environ</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>environ 1519</t>
+          <t>1519 environ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>environ 1520</t>
+          <t>1520 environ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>environ 1580</t>
+          <t>1580 environ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>environ 1480</t>
+          <t>1480 environ</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9407,17 +9407,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>environ 1445</t>
+          <t>1445 environ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>environ 1503</t>
+          <t>1503 environ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>environ 1531</t>
+          <t>1531 environ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>environ 1441</t>
+          <t>1441 environ</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>environ 1565</t>
+          <t>1565 environ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>environ 1500</t>
+          <t>1500 environ</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>environ 1566</t>
+          <t>1566 environ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10795,7 +10795,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>environ 1488</t>
+          <t>1488 environ</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>environ 1488</t>
+          <t>1488 environ</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>environ 1488</t>
+          <t>1488 environ</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
